--- a/data/trans_orig/P1418-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1418-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de mala circulación en 2007</t>
+          <t>Población con diagnóstico de mala circulación en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>96701</t>
+          <t>97284</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>134711</t>
+          <t>136676</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>211809</t>
+          <t>208381</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>266315</t>
+          <t>266242</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>318143</t>
+          <t>320086</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>387098</t>
+          <t>388749</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,56%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>897012</t>
+          <t>895047</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>935022</t>
+          <t>934439</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1048798</t>
+          <t>1048871</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1103304</t>
+          <t>1106732</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1959737</t>
+          <t>1958086</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2028692</t>
+          <t>2026749</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,36%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38460</t>
+          <t>37008</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65795</t>
+          <t>65487</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69778</t>
+          <t>67587</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>105342</t>
+          <t>107219</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>116829</t>
+          <t>114339</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>160780</t>
+          <t>161541</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1627618</t>
+          <t>1627926</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1654953</t>
+          <t>1656405</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1482331</t>
+          <t>1480454</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1517895</t>
+          <t>1520086</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3120306</t>
+          <t>3119545</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3164257</t>
+          <t>3166747</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,52%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7725</t>
+          <t>7056</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23053</t>
+          <t>23543</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12456</t>
+          <t>11301</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29738</t>
+          <t>29288</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23474</t>
+          <t>22670</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47567</t>
+          <t>47925</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>528355</t>
+          <t>527865</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>543683</t>
+          <t>544352</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>446674</t>
+          <t>447124</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>463956</t>
+          <t>465111</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>980253</t>
+          <t>979895</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1004346</t>
+          <t>1005150</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,79%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>156679</t>
+          <t>154201</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>208697</t>
+          <t>205646</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>312259</t>
+          <t>308880</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>382390</t>
+          <t>381226</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>477027</t>
+          <t>482505</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>568283</t>
+          <t>564282</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3067846</t>
+          <t>3070897</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3119864</t>
+          <t>3122342</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2996807</t>
+          <t>2997971</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3066938</t>
+          <t>3070317</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6087458</t>
+          <t>6091459</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6178714</t>
+          <t>6173236</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,75%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de mala circulación en 2012</t>
+          <t>Población con diagnóstico de mala circulación en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>61727</t>
+          <t>62373</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>95691</t>
+          <t>96889</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>219572</t>
+          <t>220080</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>280717</t>
+          <t>276523</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>292217</t>
+          <t>292656</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>361043</t>
+          <t>362882</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,69%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>878952</t>
+          <t>877754</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>912916</t>
+          <t>912270</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1057080</t>
+          <t>1061274</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1118225</t>
+          <t>1117717</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1951397</t>
+          <t>1949558</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2020223</t>
+          <t>2019784</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,34%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15679</t>
+          <t>15318</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38570</t>
+          <t>37881</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69209</t>
+          <t>69692</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>108333</t>
+          <t>110509</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>90556</t>
+          <t>90265</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>136633</t>
+          <t>136300</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1925387</t>
+          <t>1926076</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1948278</t>
+          <t>1948639</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1645212</t>
+          <t>1643036</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1684336</t>
+          <t>1683853</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3580870</t>
+          <t>3581203</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3626947</t>
+          <t>3627238</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12820</t>
+          <t>12363</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4317</t>
+          <t>4641</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16993</t>
+          <t>17094</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7370</t>
+          <t>8128</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23727</t>
+          <t>23477</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>468361</t>
+          <t>468818</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>480180</t>
+          <t>480166</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>441638</t>
+          <t>441537</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>454314</t>
+          <t>453990</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>916086</t>
+          <t>916336</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>932443</t>
+          <t>931685</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86161</t>
+          <t>87666</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>130571</t>
+          <t>126829</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>306990</t>
+          <t>310294</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>379025</t>
+          <t>383963</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>410188</t>
+          <t>413756</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>494868</t>
+          <t>495385</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3289211</t>
+          <t>3292953</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3333621</t>
+          <t>3332116</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3170948</t>
+          <t>3166010</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3242983</t>
+          <t>3239679</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6474887</t>
+          <t>6474370</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6559567</t>
+          <t>6555999</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,06%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de mala circulación en 2016</t>
+          <t>Población con diagnóstico de mala circulación en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36181</t>
+          <t>37036</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61231</t>
+          <t>61891</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>128449</t>
+          <t>127883</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>176901</t>
+          <t>175114</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>170040</t>
+          <t>169663</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>227927</t>
+          <t>229495</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>693116</t>
+          <t>692456</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>718166</t>
+          <t>717311</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>817759</t>
+          <t>819546</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>866211</t>
+          <t>866777</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1521080</t>
+          <t>1519512</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1578967</t>
+          <t>1579344</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,3%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20111</t>
+          <t>21209</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42466</t>
+          <t>44602</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69542</t>
+          <t>69879</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>108648</t>
+          <t>108596</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>97823</t>
+          <t>96107</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>141624</t>
+          <t>140844</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2033919</t>
+          <t>2031783</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2056274</t>
+          <t>2055176</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1879652</t>
+          <t>1879704</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1918758</t>
+          <t>1918421</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3923061</t>
+          <t>3923841</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3966862</t>
+          <t>3968578</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,64%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1106</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10147</t>
+          <t>10688</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6757</t>
+          <t>7022</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22320</t>
+          <t>23403</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10034</t>
+          <t>10236</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28432</t>
+          <t>27836</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>536739</t>
+          <t>536198</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>545768</t>
+          <t>545780</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>526820</t>
+          <t>525737</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>542383</t>
+          <t>542118</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1067595</t>
+          <t>1068191</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1085993</t>
+          <t>1085791</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66054</t>
+          <t>64721</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>101462</t>
+          <t>98679</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>218356</t>
+          <t>223789</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>285040</t>
+          <t>287592</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>297147</t>
+          <t>296021</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>370957</t>
+          <t>372666</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3276156</t>
+          <t>3278939</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3311564</t>
+          <t>3312897</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3247060</t>
+          <t>3244508</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3313744</t>
+          <t>3308311</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6538761</t>
+          <t>6537052</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6612571</t>
+          <t>6613697</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,72%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de mala circulación en 2023</t>
+          <t>Población con diagnóstico de mala circulación en 2023 (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51222</t>
+          <t>51525</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>78002</t>
+          <t>75715</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>134297</t>
+          <t>135260</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>169193</t>
+          <t>170037</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>192733</t>
+          <t>194607</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>238653</t>
+          <t>238415</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,85%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>434618</t>
+          <t>436905</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>461398</t>
+          <t>461095</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>582731</t>
+          <t>581887</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>617627</t>
+          <t>616664</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1025891</t>
+          <t>1026129</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1071811</t>
+          <t>1069937</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,61%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43129</t>
+          <t>43789</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>83090</t>
+          <t>83822</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>88135</t>
+          <t>88737</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>143944</t>
+          <t>145269</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>147715</t>
+          <t>140285</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>216049</t>
+          <t>213728</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2205375</t>
+          <t>2204643</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2245336</t>
+          <t>2244676</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2090089</t>
+          <t>2088764</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2145898</t>
+          <t>2145296</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4306449</t>
+          <t>4308770</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4374783</t>
+          <t>4382213</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,9%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5993</t>
+          <t>6079</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18756</t>
+          <t>19191</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22040</t>
+          <t>21430</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41689</t>
+          <t>42484</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30508</t>
+          <t>30528</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53179</t>
+          <t>55221</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>626811</t>
+          <t>626376</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>639574</t>
+          <t>639488</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>617199</t>
+          <t>616404</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>636848</t>
+          <t>637458</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1251276</t>
+          <t>1249234</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1273947</t>
+          <t>1273927</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>106104</t>
+          <t>107278</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>162017</t>
+          <t>161699</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>244293</t>
+          <t>247151</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>335078</t>
+          <t>340983</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>382369</t>
+          <t>378733</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>484304</t>
+          <t>484010</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3284635</t>
+          <t>3284953</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3340548</t>
+          <t>3339374</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3309767</t>
+          <t>3303862</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3400552</t>
+          <t>3397694</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6607193</t>
+          <t>6607487</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6709128</t>
+          <t>6712764</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,66%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1418-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1418-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>97284</t>
+          <t>97375</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>136676</t>
+          <t>136973</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>208381</t>
+          <t>211291</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>266242</t>
+          <t>268983</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>320086</t>
+          <t>320097</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>388749</t>
+          <t>386697</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,48%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>895047</t>
+          <t>894750</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>934439</t>
+          <t>934348</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1048871</t>
+          <t>1046130</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1106732</t>
+          <t>1103822</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1958086</t>
+          <t>1960138</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2026749</t>
+          <t>2026738</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37008</t>
+          <t>38179</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65487</t>
+          <t>65919</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>67587</t>
+          <t>69968</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>107219</t>
+          <t>106539</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>114339</t>
+          <t>115701</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>161541</t>
+          <t>161343</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1627926</t>
+          <t>1627494</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1656405</t>
+          <t>1655234</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1480454</t>
+          <t>1481134</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1520086</t>
+          <t>1517705</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3119545</t>
+          <t>3119743</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3166747</t>
+          <t>3165385</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,47%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7056</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23543</t>
+          <t>22864</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11301</t>
+          <t>11520</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29288</t>
+          <t>29884</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22670</t>
+          <t>24022</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47925</t>
+          <t>47242</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>527865</t>
+          <t>528544</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>544352</t>
+          <t>543580</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>447124</t>
+          <t>446528</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>465111</t>
+          <t>464892</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>979895</t>
+          <t>980578</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1005150</t>
+          <t>1003798</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,66%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>154201</t>
+          <t>156040</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>205646</t>
+          <t>206738</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>308880</t>
+          <t>309379</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>381226</t>
+          <t>378888</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>482505</t>
+          <t>475182</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>564282</t>
+          <t>565293</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3070897</t>
+          <t>3069805</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3122342</t>
+          <t>3120503</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2997971</t>
+          <t>3000309</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3070317</t>
+          <t>3069818</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6091459</t>
+          <t>6090448</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6173236</t>
+          <t>6180559</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,86%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>62373</t>
+          <t>61713</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>96889</t>
+          <t>96826</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>220080</t>
+          <t>221524</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>276523</t>
+          <t>280791</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>292656</t>
+          <t>294232</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>362882</t>
+          <t>362927</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>877754</t>
+          <t>877817</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>912270</t>
+          <t>912930</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1061274</t>
+          <t>1057006</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1117717</t>
+          <t>1116273</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1949558</t>
+          <t>1949513</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2019784</t>
+          <t>2018208</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,28%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15318</t>
+          <t>15214</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37881</t>
+          <t>36821</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69692</t>
+          <t>70899</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>110509</t>
+          <t>110738</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>90265</t>
+          <t>89285</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>136300</t>
+          <t>134688</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1926076</t>
+          <t>1927136</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1948639</t>
+          <t>1948743</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1643036</t>
+          <t>1642807</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1683853</t>
+          <t>1682646</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3581203</t>
+          <t>3582815</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3627238</t>
+          <t>3628218</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,6%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12363</t>
+          <t>13203</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4641</t>
+          <t>4275</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17094</t>
+          <t>17772</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8128</t>
+          <t>7726</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23477</t>
+          <t>23980</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>468818</t>
+          <t>467978</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>480166</t>
+          <t>479279</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>441537</t>
+          <t>440859</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>453990</t>
+          <t>454356</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>916336</t>
+          <t>915833</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>931685</t>
+          <t>932087</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>87666</t>
+          <t>89125</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>126829</t>
+          <t>131487</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>310294</t>
+          <t>311549</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>383963</t>
+          <t>384223</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>413756</t>
+          <t>410777</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>495385</t>
+          <t>498115</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3292953</t>
+          <t>3288295</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3332116</t>
+          <t>3330657</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3166010</t>
+          <t>3165750</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3239679</t>
+          <t>3238424</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6474370</t>
+          <t>6471640</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6555999</t>
+          <t>6558978</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,11%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37036</t>
+          <t>36001</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61891</t>
+          <t>62409</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>127883</t>
+          <t>130229</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>175114</t>
+          <t>177618</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>169663</t>
+          <t>174429</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>229495</t>
+          <t>227768</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,02%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>692456</t>
+          <t>691938</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>717311</t>
+          <t>718346</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>819546</t>
+          <t>817042</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>866777</t>
+          <t>864431</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1519512</t>
+          <t>1521239</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1579344</t>
+          <t>1574578</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,03%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21209</t>
+          <t>21113</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44602</t>
+          <t>43367</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69879</t>
+          <t>69020</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>108596</t>
+          <t>107262</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>96107</t>
+          <t>97434</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>140844</t>
+          <t>143713</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2031783</t>
+          <t>2033018</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2055176</t>
+          <t>2055272</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1879704</t>
+          <t>1881038</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1918421</t>
+          <t>1919280</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3923841</t>
+          <t>3920972</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3968578</t>
+          <t>3967251</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,6%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1106</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10688</t>
+          <t>11207</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7022</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23403</t>
+          <t>23553</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10236</t>
+          <t>10127</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27836</t>
+          <t>28882</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>536198</t>
+          <t>535679</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>545780</t>
+          <t>545769</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>525737</t>
+          <t>525587</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>542118</t>
+          <t>541839</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1068191</t>
+          <t>1067145</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1085791</t>
+          <t>1085900</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64721</t>
+          <t>65059</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>98679</t>
+          <t>101400</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>223789</t>
+          <t>221657</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>287592</t>
+          <t>286312</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>296021</t>
+          <t>296479</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>372666</t>
+          <t>374582</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3278939</t>
+          <t>3276218</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3312897</t>
+          <t>3312559</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3244508</t>
+          <t>3245788</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3308311</t>
+          <t>3310443</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6537052</t>
+          <t>6535136</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6613697</t>
+          <t>6613239</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,71%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>63051</t>
+          <t>67091</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51525</t>
+          <t>53787</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>75715</t>
+          <t>81238</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>150721</t>
+          <t>160263</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>135260</t>
+          <t>143349</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>170037</t>
+          <t>178381</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>213772</t>
+          <t>227355</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>194607</t>
+          <t>207703</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>238415</t>
+          <t>249654</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>17,88%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>449569</t>
+          <t>509052</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>436905</t>
+          <t>494905</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>461095</t>
+          <t>522356</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>601203</t>
+          <t>659690</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>581887</t>
+          <t>641572</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>616664</t>
+          <t>676604</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1050772</t>
+          <t>1168742</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1026129</t>
+          <t>1146443</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1069937</t>
+          <t>1188394</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>85,12%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>512620</t>
+          <t>576143</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>512620</t>
+          <t>576143</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>512620</t>
+          <t>576143</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>751924</t>
+          <t>819953</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>751924</t>
+          <t>819953</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>751924</t>
+          <t>819953</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1264544</t>
+          <t>1396097</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1264544</t>
+          <t>1396097</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1264544</t>
+          <t>1396097</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>64004</t>
+          <t>69509</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43789</t>
+          <t>53573</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>83822</t>
+          <t>89241</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>120422</t>
+          <t>132770</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>88737</t>
+          <t>115209</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>145269</t>
+          <t>151441</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>184426</t>
+          <t>202279</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>140285</t>
+          <t>178717</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>213728</t>
+          <t>229208</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2224461</t>
+          <t>2159056</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2204643</t>
+          <t>2139324</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2244676</t>
+          <t>2174992</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2113611</t>
+          <t>2033952</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2088764</t>
+          <t>2015281</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2145296</t>
+          <t>2051513</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4338072</t>
+          <t>4193008</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4308770</t>
+          <t>4166079</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4382213</t>
+          <t>4216570</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>95,93%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2288465</t>
+          <t>2228565</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2288465</t>
+          <t>2228565</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2288465</t>
+          <t>2228565</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2234033</t>
+          <t>2166722</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2234033</t>
+          <t>2166722</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2234033</t>
+          <t>2166722</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4522498</t>
+          <t>4395287</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4522498</t>
+          <t>4395287</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4522498</t>
+          <t>4395287</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>11071</t>
+          <t>11439</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6079</t>
+          <t>6351</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19191</t>
+          <t>18625</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>30194</t>
+          <t>34527</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21430</t>
+          <t>25986</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42484</t>
+          <t>47064</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>41265</t>
+          <t>45967</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30528</t>
+          <t>35089</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55221</t>
+          <t>60091</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>634496</t>
+          <t>699052</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>626376</t>
+          <t>691866</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>639488</t>
+          <t>704140</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>628694</t>
+          <t>698241</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>616404</t>
+          <t>685704</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>637458</t>
+          <t>706782</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1263190</t>
+          <t>1397292</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1249234</t>
+          <t>1383168</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1273927</t>
+          <t>1408170</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>645567</t>
+          <t>710491</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>645567</t>
+          <t>710491</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>645567</t>
+          <t>710491</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>658888</t>
+          <t>732768</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>658888</t>
+          <t>732768</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>658888</t>
+          <t>732768</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1304455</t>
+          <t>1443259</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1304455</t>
+          <t>1443259</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1304455</t>
+          <t>1443259</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>138127</t>
+          <t>148039</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>107278</t>
+          <t>128878</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>161699</t>
+          <t>173553</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>301337</t>
+          <t>327560</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>247151</t>
+          <t>300544</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>340983</t>
+          <t>354285</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>439464</t>
+          <t>475600</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>378733</t>
+          <t>440094</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>484010</t>
+          <t>513254</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3308525</t>
+          <t>3367161</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3284953</t>
+          <t>3341647</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3339374</t>
+          <t>3386322</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3343508</t>
+          <t>3391883</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3303862</t>
+          <t>3365158</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3397694</t>
+          <t>3418899</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6652033</t>
+          <t>6759043</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6607487</t>
+          <t>6721389</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6712764</t>
+          <t>6794549</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>93,92%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3446652</t>
+          <t>3515200</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3446652</t>
+          <t>3515200</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3446652</t>
+          <t>3515200</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3644845</t>
+          <t>3719443</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3644845</t>
+          <t>3719443</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3644845</t>
+          <t>3719443</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7091497</t>
+          <t>7234643</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7091497</t>
+          <t>7234643</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7091497</t>
+          <t>7234643</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
